--- a/verification/revamp-R6/artifacts/mobile-profitlens.xlsx
+++ b/verification/revamp-R6/artifacts/mobile-profitlens.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="106">
   <si>
     <t>區塊</t>
   </si>
@@ -132,33 +132,6 @@
   </si>
   <si>
     <t>下一步：比對各媒體的 ROAS，先縮減表現最差的活動，設定每週檢查點</t>
-  </si>
-  <si>
-    <t>會議紀錄</t>
-  </si>
-  <si>
-    <t>會議名稱</t>
-  </si>
-  <si>
-    <t>本期營運會議</t>
-  </si>
-  <si>
-    <t>會議日期</t>
-  </si>
-  <si>
-    <t>2026-10-03</t>
-  </si>
-  <si>
-    <t>決議</t>
-  </si>
-  <si>
-    <t>草稿</t>
-  </si>
-  <si>
-    <t>備註</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>上期淨營收</t>
@@ -755,7 +728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H13"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="51.83203125" customWidth="1"/>
@@ -961,53 +934,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" t="s">
-        <v>33</v>
-      </c>
-      <c r="H14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" t="s">
-        <v>35</v>
-      </c>
-      <c r="H15" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" t="s">
-        <v>37</v>
-      </c>
-      <c r="H16" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" t="s">
-        <v>39</v>
-      </c>
-      <c r="H17" t="s">
-        <v>40</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1031,30 +960,30 @@
         <v>19</v>
       </c>
       <c r="B1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="C1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B2" s="1">
         <v>1350</v>
@@ -1075,12 +1004,12 @@
         <v>-130</v>
       </c>
       <c r="H2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B3" s="1">
         <v>900</v>
@@ -1101,12 +1030,12 @@
         <v>-185</v>
       </c>
       <c r="H3" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B4" s="1">
         <v>2250</v>
@@ -1127,7 +1056,7 @@
         <v>-315</v>
       </c>
       <c r="H4" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1162,7 +1091,7 @@
         <v>6</v>
       </c>
       <c r="E1" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
@@ -1179,12 +1108,12 @@
         <v>-315</v>
       </c>
       <c r="E2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B3" s="1">
         <v>2500</v>
@@ -1196,12 +1125,12 @@
         <v>600</v>
       </c>
       <c r="E3" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B4" s="1">
         <v>200</v>
@@ -1213,12 +1142,12 @@
         <v>-250</v>
       </c>
       <c r="E4" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B5" s="1">
         <v>50</v>
@@ -1230,12 +1159,12 @@
         <v>-130</v>
       </c>
       <c r="E5" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B6" s="1">
         <v>1050</v>
@@ -1247,12 +1176,12 @@
         <v>-275</v>
       </c>
       <c r="E6" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B7" s="1">
         <v>90</v>
@@ -1264,12 +1193,12 @@
         <v>-30</v>
       </c>
       <c r="E7" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="B8" s="1">
         <v>60</v>
@@ -1281,12 +1210,12 @@
         <v>-6</v>
       </c>
       <c r="E8" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B9" s="1">
         <v>160</v>
@@ -1298,12 +1227,12 @@
         <v>-65</v>
       </c>
       <c r="E9" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B10" s="1">
         <v>20</v>
@@ -1315,12 +1244,12 @@
         <v>-9</v>
       </c>
       <c r="E10" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="B11" s="1">
         <v>300</v>
@@ -1332,18 +1261,18 @@
         <v>-150</v>
       </c>
       <c r="E11" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D12" s="1">
         <v>-315</v>
       </c>
       <c r="E12" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1375,45 +1304,45 @@
         <v>19</v>
       </c>
       <c r="B1" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D1" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="F1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G1" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="H1" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="I1" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D2" s="2">
         <v>3</v>
@@ -1437,18 +1366,18 @@
         <v>40</v>
       </c>
       <c r="K2" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -1472,18 +1401,18 @@
         <v>-50</v>
       </c>
       <c r="K3" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D4" s="2">
         <v>3</v>
@@ -1507,18 +1436,18 @@
         <v>10</v>
       </c>
       <c r="K4" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
@@ -1542,7 +1471,7 @@
         <v>-55</v>
       </c>
       <c r="K5" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1571,37 +1500,37 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="B1" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C1" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D1" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="E1" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="F1" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G1" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H1" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I1" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="J1" t="s">
         <v>2</v>
       </c>
       <c r="K1" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1633,93 +1562,93 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" t="s">
         <v>89</v>
-      </c>
-      <c r="C10" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B12" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
@@ -1727,68 +1656,68 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B13" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B14" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C14" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B15" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="C15" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>92</v>
+      </c>
+      <c r="B16" t="s">
+        <v>100</v>
+      </c>
+      <c r="C16" t="s">
         <v>101</v>
-      </c>
-      <c r="B16" t="s">
-        <v>109</v>
-      </c>
-      <c r="C16" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B17" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="C17" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B18" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="C18" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
